--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/03_Politika, Hedefler ve Yönetim/EKG-YNT-FRM-02_yonetimin_gozden_gecirmesi_tutanagi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/03_Politika, Hedefler ve Yönetim/EKG-YNT-FRM-02_yonetimin_gozden_gecirmesi_tutanagi.xlsx
@@ -805,7 +805,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Yönetimin Gözden Geçirmesi Tutanağı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: YGG tutanağına bağlam, ilgili taraf ve risk/fırsat değişiklikleri gündemi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R383af0a0f34a47d4"/>
   <x:tableParts count="1">
@@ -1134,7 +1135,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-FRM-02&amp;C&amp;"Arial,Regular"&amp;11Yönetimin Gözden Geçirmesi Tutanağı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: YGG tutanağına bağlam, ilgili taraf ve risk/fırsat değişiklikleri gündemi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9db7c59d1e8447c"/>
   <x:tableParts count="1">
